--- a/manual.xlsx
+++ b/manual.xlsx
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
-  <si>
-    <t>en valores tener en cuenta que el valor por defecto que usa el sistema es el primero que se carga al configurar el sistema</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Valores</t>
   </si>
@@ -96,6 +93,21 @@
   </si>
   <si>
     <t>OJO en eccomerce configura con el primer registro</t>
+  </si>
+  <si>
+    <t>entradas y remitos usan el mismo numerador</t>
+  </si>
+  <si>
+    <t>los valores en escribania son sin ivaen las diligencias y en las entradas con iva incluido</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>en valores tener en cuenta que el valor por defecto que usa el sistema es el primero que se carga al configurar el sistema es el primero en orden alfavetico</t>
+  </si>
+  <si>
+    <t>recibos y ordenes de pago usas mismo numerador</t>
   </si>
 </sst>
 </file>
@@ -481,116 +493,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
         <v>3</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>4</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
         <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
